--- a/reports/集团总公司_利润表_2025-08.xlsx
+++ b/reports/集团总公司_利润表_2025-08.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>245514098</v>
+        <v>267738556</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>186726221</v>
+        <v>202835352</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1344124552</v>
+        <v>1459000877</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>764999</v>
+        <v>982097</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>5482385</v>
+        <v>7090539</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>661623</v>
+        <v>860476</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4756589</v>
+        <v>6204657</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>562224</v>
+        <v>727562</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4030874</v>
+        <v>5238257</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>514218</v>
+        <v>672778</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3708014</v>
+        <v>4835961</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>280353</v>
+        <v>370632</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2014987</v>
+        <v>2660157</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>222999</v>
+        <v>292318</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1611826</v>
+        <v>2096107</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>242507682</v>
+        <v>263832693</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>183719805</v>
+        <v>198929489</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>94151546</v>
+        <v>104121413</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>680770272</v>
+        <v>745849482</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1731411</v>
+        <v>3080526</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>12489276</v>
+        <v>22167116</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1563972</v>
+        <v>2237713</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>11282130</v>
+        <v>16120252</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>84407361</v>
+        <v>88111552</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>604513143</v>
+        <v>636601590</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1785569</v>
+        <v>2229698</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>12896244</v>
+        <v>16115123</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>788339</v>
+        <v>1115146</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>5642693</v>
+        <v>8057349</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2791115</v>
+        <v>3344977</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>20151937</v>
+        <v>24170636</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1238319</v>
+        <v>1674853</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>8868133</v>
+        <v>12086445</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>58617915</v>
+        <v>58781768</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>421564445</v>
+        <v>421606548</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169962</v>
+        <v>170275</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1360013</v>
+        <v>1360226</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3568794</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>25632463</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2382367</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>17090455</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>177268186</v>
+        <v>201595640</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>142377460</v>
+        <v>150902230</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>112142630</v>
+        <v>120632750</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>807020106</v>
+        <v>864364175</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>30234830</v>
+        <v>30269480</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>218428377</v>
+        <v>218406277</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5938612</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>42723511</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1897024</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>13669684</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1183831</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>8542412</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1419140</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>10249775</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1063987</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>7686830</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>709606</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5124501</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>591971</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4270619</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3321429</v>
+        <v>3303355</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>23779956</v>
+        <v>23774427</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1554303</v>
+        <v>1554915</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>11205200</v>
+        <v>11201107</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>4041865</v>
+        <v>4049501</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>29015791</v>
+        <v>29024551</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>26058532</v>
+        <v>26208847</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>187802314</v>
+        <v>187859650</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349389</v>
+        <v>3203506</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2799344</v>
+        <v>22979195</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1119511</v>
+        <v>1124030</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>8959016</v>
+        <v>8962129</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1154960</v>
+        <v>1072963</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>9278426</v>
+        <v>8561538</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>120067</v>
+        <v>120269</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>959882</v>
+        <v>960114</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>477097</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3815846</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>1037203</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>7475472</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>317044</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2543346</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>237559</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1907413</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>395833</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3179041</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1478505</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>10676074</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>211458</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1695760</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>158846</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1271976</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>265211</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2120237</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>185949</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1484329</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132979</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1060308</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>106443</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>848264</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79819</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>636176</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>65239496</v>
+        <v>65759350</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>70192834</v>
+        <v>70059089</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>593581</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4272204</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132267</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1059810</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>210651</v>
+        <v>209338</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1680163</v>
+        <v>1679553</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>65028845</v>
+        <v>66143593</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7139712</v>
+        <v>7069747</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>56809942</v>
+        <v>56782610</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>57889133</v>
+        <v>59073846</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>57889133</v>
+        <v>59073846</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>57889133</v>
+        <v>59073846</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>57889133</v>
+        <v>59073846</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>57889133</v>
+        <v>59073846</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
